--- a/Configs/GameConfig/Datas/i18n.xlsx
+++ b/Configs/GameConfig/Datas/i18n.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23610" windowHeight="14400"/>
+    <workbookView windowWidth="30240" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="116">
   <si>
     <t>##var</t>
   </si>
@@ -393,6 +393,27 @@
   </si>
   <si>
     <t>確定</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>音乐</t>
+  </si>
+  <si>
+    <t>音樂</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>audio</t>
+  </si>
+  <si>
+    <t>音效</t>
+  </si>
+  <si>
+    <t>Autdio</t>
   </si>
 </sst>
 </file>
@@ -1041,12 +1062,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1366,14 +1387,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:AA32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="9.225" customWidth="1"/>
+    <col min="1" max="1" width="9.22321428571429" customWidth="1"/>
     <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="3" width="40.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="35.4166666666667" customWidth="1"/>
-    <col min="5" max="5" width="53.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="40.8303571428571" customWidth="1"/>
+    <col min="4" max="4" width="35.4196428571429" customWidth="1"/>
+    <col min="5" max="5" width="53.6696428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:27">
@@ -1392,7 +1413,7 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4"/>
+      <c r="F1" s="7"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
@@ -1423,7 +1444,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
+      <c r="F2" s="7"/>
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2"/>
@@ -1447,22 +1468,22 @@
       <c r="AA2"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:27">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="7"/>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
@@ -1501,7 +1522,7 @@
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="7"/>
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4"/>
@@ -1524,17 +1545,17 @@
       <c r="Z4"/>
       <c r="AA4"/>
     </row>
-    <row r="5" ht="28" spans="2:5">
+    <row r="5" ht="34" spans="2:5">
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1552,14 +1573,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" ht="17" spans="2:5">
       <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E7" t="s">
@@ -1598,7 +1619,7 @@
       <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>33</v>
       </c>
       <c r="D10" t="s">
@@ -1636,73 +1657,73 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" ht="17" spans="2:5">
       <c r="B13" t="s">
         <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>46</v>
       </c>
       <c r="E13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="56" spans="2:5">
+    <row r="14" ht="68" spans="2:5">
       <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" ht="266" spans="2:5">
+    <row r="15" ht="320" spans="2:5">
       <c r="B15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" ht="28" spans="2:5">
+    <row r="16" ht="34" spans="2:5">
       <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" ht="168" spans="2:5">
+    <row r="17" ht="236" spans="2:5">
       <c r="B17" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1748,14 +1769,14 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" ht="17" spans="2:5">
       <c r="B21" t="s">
         <v>74</v>
       </c>
       <c r="C21" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E21" t="s">
@@ -1846,14 +1867,14 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" ht="17" spans="2:5">
       <c r="B28" t="s">
         <v>99</v>
       </c>
       <c r="C28" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E28" t="s">
@@ -1886,6 +1907,31 @@
       </c>
       <c r="E30" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/i18n.xlsx
+++ b/Configs/GameConfig/Datas/i18n.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12960"/>
+    <workbookView windowWidth="30240" windowHeight="12840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="116">
   <si>
     <t>##var</t>
   </si>
@@ -1930,6 +1930,9 @@
       <c r="C32" t="s">
         <v>114</v>
       </c>
+      <c r="D32" t="s">
+        <v>114</v>
+      </c>
       <c r="E32" t="s">
         <v>115</v>
       </c>

--- a/Configs/GameConfig/Datas/i18n.xlsx
+++ b/Configs/GameConfig/Datas/i18n.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12840"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="131">
   <si>
     <t>##var</t>
   </si>
@@ -414,6 +414,51 @@
   </si>
   <si>
     <t>Autdio</t>
+  </si>
+  <si>
+    <t>chupin</t>
+  </si>
+  <si>
+    <t>出品</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>cehua</t>
+  </si>
+  <si>
+    <t>策划</t>
+  </si>
+  <si>
+    <t>策劃</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>chengxu</t>
+  </si>
+  <si>
+    <t>程序、</t>
+  </si>
+  <si>
+    <t>程式</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>art</t>
+  </si>
+  <si>
+    <t>美术</t>
+  </si>
+  <si>
+    <t>美術</t>
+  </si>
+  <si>
+    <t>Arts</t>
   </si>
 </sst>
 </file>
@@ -1057,17 +1102,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1387,14 +1435,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:AA36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.22321428571429" customWidth="1"/>
+    <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="3" width="40.8303571428571" customWidth="1"/>
-    <col min="4" max="4" width="35.4196428571429" customWidth="1"/>
-    <col min="5" max="5" width="53.6696428571429" customWidth="1"/>
+    <col min="3" max="3" width="40.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="35.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="53.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:27">
@@ -1413,7 +1461,7 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7"/>
+      <c r="F1" s="4"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
@@ -1444,7 +1492,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="7"/>
+      <c r="F2" s="4"/>
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2"/>
@@ -1468,22 +1516,22 @@
       <c r="AA2"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:27">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="7"/>
+      <c r="F3" s="4"/>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
@@ -1522,7 +1570,7 @@
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="4"/>
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4"/>
@@ -1545,17 +1593,17 @@
       <c r="Z4"/>
       <c r="AA4"/>
     </row>
-    <row r="5" ht="34" spans="2:5">
+    <row r="5" ht="28" spans="2:5">
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1573,14 +1621,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="17" spans="2:5">
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" t="s">
@@ -1619,7 +1667,7 @@
       <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D10" t="s">
@@ -1657,73 +1705,73 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="2:5">
+    <row r="13" spans="2:5">
       <c r="B13" t="s">
         <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>46</v>
       </c>
       <c r="E13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="68" spans="2:5">
+    <row r="14" ht="56" spans="2:5">
       <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" ht="320" spans="2:5">
+    <row r="15" ht="266" spans="2:5">
       <c r="B15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" ht="34" spans="2:5">
+    <row r="16" ht="28" spans="2:5">
       <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" ht="236" spans="2:5">
+    <row r="17" ht="168" spans="2:5">
       <c r="B17" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1769,14 +1817,14 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" ht="17" spans="2:5">
+    <row r="21" spans="2:5">
       <c r="B21" t="s">
         <v>74</v>
       </c>
       <c r="C21" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E21" t="s">
@@ -1867,14 +1915,14 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" ht="17" spans="2:5">
+    <row r="28" spans="2:5">
       <c r="B28" t="s">
         <v>99</v>
       </c>
       <c r="C28" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E28" t="s">
@@ -1935,6 +1983,62 @@
       </c>
       <c r="E32" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/i18n.xlsx
+++ b/Configs/GameConfig/Datas/i18n.xlsx
@@ -440,7 +440,7 @@
     <t>chengxu</t>
   </si>
   <si>
-    <t>程序、</t>
+    <t>程序</t>
   </si>
   <si>
     <t>程式</t>
@@ -1102,7 +1102,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
@@ -1113,9 +1113,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1992,7 +1989,7 @@
       <c r="C33" t="s">
         <v>117</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="6" t="s">
         <v>117</v>
       </c>
       <c r="E33" t="s">
